--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103857</t>
+    <t>20250616134739</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:57+01:00</t>
+    <t>2025-06-16T13:47:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251028115832</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-10-28T11:58:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>34338003</t>
   </si>
   <si>
-    <t>dans les deux oreilles</t>
+    <t>les deux oreilles</t>
   </si>
   <si>
     <t>244506005</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251028115832</t>
+    <t>20251216141838</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T11:58:32+01:00</t>
+    <t>2025-12-16T14:18:38+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142103</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142103</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:03+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-human-substance-administration-site-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134041</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:41+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -234,13 +234,13 @@
     <t>1290032005</t>
   </si>
   <si>
-    <t>œil droit</t>
+    <t>œil droit proprement dit</t>
   </si>
   <si>
     <t>1290031003</t>
   </si>
   <si>
-    <t>œil gauche</t>
+    <t>œil gauche proprement dit</t>
   </si>
   <si>
     <t>40638003</t>
@@ -282,7 +282,7 @@
     <t>16217661000119109</t>
   </si>
   <si>
-    <t>deltoïde droit</t>
+    <t>deltoïde droit</t>
   </si>
   <si>
     <t>25577004</t>
